--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487398_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487398_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3675</v>
+        <v>3.9326</v>
       </c>
       <c r="E2" t="n">
-        <v>2.3585</v>
+        <v>2.8702</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0089</v>
+        <v>1.0624</v>
       </c>
       <c r="G2" t="n">
         <v>3.2307</v>
@@ -610,13 +610,13 @@
         <v>0.5875</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4507</v>
+        <v>0.1144</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4576</v>
+        <v>0.0541</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0068</v>
+        <v>0.0603</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. VALDES ALVAREZ</t>
+          <t>A. IGLESIAS CAMINO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3063</v>
+        <v>1.6972</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2053</v>
+        <v>0.0554</v>
       </c>
       <c r="F3" t="n">
-        <v>0.101</v>
+        <v>1.6418</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0649</v>
+        <v>2.9421</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7524</v>
+        <v>-2.8473</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.6874</v>
+        <v>5.7894</v>
       </c>
       <c r="J3" t="n">
-        <v>2.4221</v>
+        <v>3.7441</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5845</v>
+        <v>-0.6756</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.1624</v>
+        <v>4.4197</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.3572</v>
+        <v>-0.8021</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.8322</v>
+        <v>-2.1717</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.525</v>
+        <v>1.3697</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1751</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9792</v>
+        <v>-2.9377</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1543</v>
+        <v>1.7626</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1239</v>
+        <v>-0.0698</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.18</v>
+        <v>-0.7511</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3038</v>
+        <v>0.6812</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.0576</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.0576</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. IGLESIAS CAMINO</t>
+          <t>C. VALDES ALVAREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2214</v>
+        <v>0.8052</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.661</v>
+        <v>0.6506999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8824</v>
+        <v>0.1545</v>
       </c>
       <c r="G4" t="n">
-        <v>2.9421</v>
+        <v>0.0649</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.8473</v>
+        <v>1.7524</v>
       </c>
       <c r="I4" t="n">
-        <v>5.7894</v>
+        <v>-1.6874</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7441</v>
+        <v>2.4221</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6756</v>
+        <v>3.5845</v>
       </c>
       <c r="L4" t="n">
-        <v>4.4197</v>
+        <v>-1.1624</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8021</v>
+        <v>-2.3572</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.1717</v>
+        <v>-1.8322</v>
       </c>
       <c r="O4" t="n">
-        <v>1.3697</v>
+        <v>-0.525</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.1751</v>
+        <v>1.1751</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.9377</v>
+        <v>-0.9792</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7626</v>
+        <v>2.1543</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5456</v>
+        <v>-0.3773</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.4674</v>
+        <v>-0.7346</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9218</v>
+        <v>0.3573</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.0576</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.0576</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. GARCIA ORTIZ</t>
+          <t>A. BELLON LOPEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2842</v>
+        <v>0.0854</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1921</v>
+        <v>0.2876</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4763</v>
+        <v>-0.2022</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5089</v>
+        <v>0.1214</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.949</v>
+        <v>0.2375</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4401</v>
+        <v>-0.1161</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1609</v>
+        <v>1.262</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.7282999999999999</v>
+        <v>0.575</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8891</v>
+        <v>0.6871</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6698</v>
+        <v>-1.1406</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2207</v>
+        <v>-0.3375</v>
       </c>
       <c r="O5" t="n">
-        <v>0.551</v>
+        <v>-0.8031</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1958</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1751</v>
+        <v>0.9792</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2631</v>
+        <v>-0.3114</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2921</v>
+        <v>-0.2705</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.029</v>
+        <v>-0.0409</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6659</v>
+        <v>0.2754</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6659</v>
+        <v>0.2754</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. BELLON LOPEZ</t>
+          <t>L. GARCÍA SINDIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1252</v>
+        <v>-0.1141</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0235</v>
+        <v>0.6622</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1488</v>
+        <v>-0.7763</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1214</v>
+        <v>0.7734</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2375</v>
+        <v>-0.9789</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1161</v>
+        <v>1.7523</v>
       </c>
       <c r="J6" t="n">
-        <v>1.262</v>
+        <v>1.1109</v>
       </c>
       <c r="K6" t="n">
-        <v>0.575</v>
+        <v>0.0408</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6871</v>
+        <v>1.0701</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1406</v>
+        <v>-0.3375</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3375</v>
+        <v>-1.0197</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8031</v>
+        <v>0.6822</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.5875</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9792</v>
+        <v>0.5875</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.522</v>
+        <v>-0.2585</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5346</v>
+        <v>-0.4488</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0126</v>
+        <v>0.1903</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2754</v>
+        <v>-1.2166</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. GIL REY</t>
+          <t>L. GARCIA ORTIZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2219</v>
+        <v>-0.4986</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-1.2155</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1223</v>
+        <v>0.7169</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1119</v>
+        <v>-0.5089</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1558</v>
+        <v>-1.949</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2677</v>
+        <v>1.4401</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7537</v>
+        <v>0.1609</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6277</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1261</v>
+        <v>0.8891</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8656</v>
+        <v>-0.6698</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4718</v>
+        <v>-1.2207</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3938</v>
+        <v>0.551</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3917</v>
+        <v>0.1958</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3709</v>
+        <v>1.1751</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4396</v>
+        <v>0.4804</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1494</v>
+        <v>0.2688</v>
       </c>
       <c r="U7" t="n">
-        <v>0.589</v>
+        <v>0.2116</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9412</v>
+        <v>-0.6659</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2754</v>
+        <v>-0.6659</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. GARCÍA SINDIN</t>
+          <t>C. GIL REY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4792</v>
+        <v>-0.5856</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4575</v>
+        <v>-0.1425</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9367</v>
+        <v>-0.4431</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7734</v>
+        <v>-0.1119</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9789</v>
+        <v>0.1558</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7523</v>
+        <v>-0.2677</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1109</v>
+        <v>0.7537</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0408</v>
+        <v>0.6277</v>
       </c>
       <c r="L8" t="n">
-        <v>1.0701</v>
+        <v>0.1261</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3375</v>
+        <v>-0.8656</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0197</v>
+        <v>-0.4718</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6822</v>
+        <v>-0.3938</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5875</v>
+        <v>0.3917</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5875</v>
+        <v>1.3709</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6235000000000001</v>
+        <v>0.0759</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6534</v>
+        <v>-0.1923</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0299</v>
+        <v>0.2682</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2166</v>
+        <v>-0.9412</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X8" t="n">
         <v>-1.2166</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5201</v>
+        <v>-1.9256</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.6694</v>
+        <v>-2.567</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1493</v>
+        <v>0.6414</v>
       </c>
       <c r="G9" t="n">
         <v>0.4556</v>
@@ -1156,13 +1156,13 @@
         <v>1.7626</v>
       </c>
       <c r="S9" t="n">
-        <v>0.416</v>
+        <v>0.0104</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7852</v>
+        <v>-0.6828</v>
       </c>
       <c r="U9" t="n">
-        <v>1.2012</v>
+        <v>0.6933</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2166</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6989</v>
+        <v>-3.1897</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7936</v>
+        <v>-1.6319</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9053</v>
+        <v>-1.5578</v>
       </c>
       <c r="G10" t="n">
         <v>-2.7667</v>
@@ -1234,13 +1234,13 @@
         <v>1.7626</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7364000000000001</v>
+        <v>-0.2272</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3694</v>
+        <v>-0.2076</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3671</v>
+        <v>-0.0196</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0175</v>
+        <v>-3.7931</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2012</v>
+        <v>-3.2442</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8162</v>
+        <v>-0.5489000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>-0.9712</v>
@@ -1312,13 +1312,13 @@
         <v>1.5668</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8493000000000001</v>
+        <v>-0.6249</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5652</v>
+        <v>-0.6081</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2841</v>
+        <v>-0.0168</v>
       </c>
       <c r="V11" t="n">
         <v>-0.8260999999999999</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.8834</v>
+        <v>-3.5863</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.572000000000001</v>
+        <v>-4.275</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6886000000000003</v>
+        <v>0.6887000000000002</v>
       </c>
       <c r="G12" t="n">
         <v>3.2294</v>
@@ -1390,10 +1390,10 @@
         <v>13.7091</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.4849</v>
+        <v>-1.188</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.8701</v>
+        <v>-3.5729</v>
       </c>
       <c r="U12" t="n">
         <v>2.3849</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.6609</v>
+        <v>4.3358</v>
       </c>
       <c r="E13" t="n">
-        <v>4.0007</v>
+        <v>4.5124</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3398</v>
+        <v>-0.1766</v>
       </c>
       <c r="G13" t="n">
         <v>0.06660000000000001</v>
@@ -1468,13 +1468,13 @@
         <v>2.7419</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8008999999999999</v>
+        <v>-0.126</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1351</v>
+        <v>-0.6234</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3342</v>
+        <v>0.4974</v>
       </c>
       <c r="V13" t="n">
         <v>4.5911</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. RUANO MARTINEZ</t>
+          <t>J. ARGENTI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.1629</v>
+        <v>1.7751</v>
       </c>
       <c r="E14" t="n">
-        <v>1.168</v>
+        <v>1.0589</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9949</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3859</v>
+        <v>0.1654</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9513</v>
+        <v>1.4386</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.5654</v>
+        <v>-1.2733</v>
       </c>
       <c r="J14" t="n">
-        <v>2.7202</v>
+        <v>1.3612</v>
       </c>
       <c r="K14" t="n">
-        <v>2.5586</v>
+        <v>2.1146</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1617</v>
+        <v>-0.7534</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.3343</v>
+        <v>-1.1958</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6073</v>
+        <v>-0.676</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.7271</v>
+        <v>-0.5198</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1958</v>
+        <v>1.5668</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1543</v>
+        <v>1.5668</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5225</v>
+        <v>0.0429</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0722</v>
+        <v>-0.3023</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4503</v>
+        <v>0.3452</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.9412</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.6659</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. SYTAR</t>
+          <t>M. FERNANDEZ ZAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3213</v>
+        <v>1.3098</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0799</v>
+        <v>1.4612</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2414</v>
+        <v>-0.1514</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2632</v>
+        <v>0.9478</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5247</v>
+        <v>0.4577</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.7879</v>
+        <v>0.4902</v>
       </c>
       <c r="J15" t="n">
-        <v>1.3941</v>
+        <v>1.6812</v>
       </c>
       <c r="K15" t="n">
-        <v>1.9955</v>
+        <v>0.3879</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6014</v>
+        <v>1.2933</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.6573</v>
+        <v>-0.7333</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4708</v>
+        <v>0.0698</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.1865</v>
+        <v>-0.8031</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.3709</v>
+        <v>0.3917</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9377</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5668</v>
+        <v>0.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7389</v>
+        <v>-0.0297</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1316</v>
+        <v>-0.22</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6073</v>
+        <v>0.1903</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.492</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. FERNANDEZ ZAS</t>
+          <t>M. RUANO MARTINEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1495</v>
+        <v>0.5828</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4612</v>
+        <v>0.0423</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3118</v>
+        <v>0.5405</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9478</v>
+        <v>0.3859</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4577</v>
+        <v>1.9513</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4902</v>
+        <v>-1.5654</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6812</v>
+        <v>2.7202</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3879</v>
+        <v>2.5586</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2933</v>
+        <v>0.1617</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7333</v>
+        <v>-2.3343</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0698</v>
+        <v>-0.6073</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8031</v>
+        <v>-1.7271</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3917</v>
+        <v>0.1958</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3917</v>
+        <v>2.1543</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1901</v>
+        <v>0.9423</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.22</v>
+        <v>-0.0535</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0299</v>
+        <v>0.9959</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.9412</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-0.6659</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. ARGENTI</t>
+          <t>A. HERMIDA PEREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7288</v>
+        <v>0.5324</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5472</v>
+        <v>-1.0238</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1816</v>
+        <v>1.5562</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1654</v>
+        <v>1.1682</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4386</v>
+        <v>0.8145</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.2733</v>
+        <v>0.3537</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3612</v>
+        <v>2.1568</v>
       </c>
       <c r="K17" t="n">
-        <v>2.1146</v>
+        <v>0.3333</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7534</v>
+        <v>1.8235</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1958</v>
+        <v>-0.9886</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.676</v>
+        <v>0.4812</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5198</v>
+        <v>-1.4698</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5668</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.9377</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5668</v>
+        <v>1.9585</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0034</v>
+        <v>0.0104</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8139999999999999</v>
+        <v>-0.2429</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1894</v>
+        <v>0.2533</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.3329</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.3329</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. HERMIDA PEREZ</t>
+          <t>A. SYTAR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6762</v>
+        <v>0.4252</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7168</v>
+        <v>0.2612</v>
       </c>
       <c r="F18" t="n">
-        <v>1.393</v>
+        <v>0.164</v>
       </c>
       <c r="G18" t="n">
-        <v>1.1682</v>
+        <v>-0.2632</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8145</v>
+        <v>1.5247</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3537</v>
+        <v>-1.7879</v>
       </c>
       <c r="J18" t="n">
-        <v>2.1568</v>
+        <v>1.3941</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3333</v>
+        <v>1.9955</v>
       </c>
       <c r="L18" t="n">
-        <v>1.8235</v>
+        <v>-0.6014</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9886</v>
+        <v>-1.6573</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4812</v>
+        <v>-0.4708</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.4698</v>
+        <v>-1.1865</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9792</v>
+        <v>-1.3709</v>
       </c>
       <c r="Q18" t="n">
         <v>-2.9377</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9585</v>
+        <v>1.5668</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1543</v>
+        <v>0.8428</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0641</v>
+        <v>0.3129</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0902</v>
+        <v>0.5299</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3329</v>
+        <v>1.2166</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.492</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3329</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. RAMOS DA CONCEIÇAO</t>
+          <t>C. DARRIBA VAZQUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3542</v>
+        <v>-0.0054</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9162</v>
+        <v>-1.1769</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2703</v>
+        <v>1.1715</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7566000000000001</v>
+        <v>1.2407</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6254</v>
+        <v>0.9626</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1313</v>
+        <v>0.2781</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5597</v>
+        <v>1.0939</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5597</v>
+        <v>1.0939</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1969</v>
+        <v>0.1468</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.1312</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1313</v>
+        <v>0.2781</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1958</v>
+        <v>-1.5668</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1958</v>
+        <v>0.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>0.915</v>
+        <v>0.3207</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3564</v>
+        <v>-0.3123</v>
       </c>
       <c r="U19" t="n">
-        <v>1.2714</v>
+        <v>0.633</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. DARRIBA VAZQUEZ</t>
+          <t>S. RAMOS DA CONCEIÇAO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5336</v>
+        <v>-0.1048</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3816</v>
+        <v>-0.8138</v>
       </c>
       <c r="F20" t="n">
-        <v>0.848</v>
+        <v>0.709</v>
       </c>
       <c r="G20" t="n">
-        <v>1.2407</v>
+        <v>-0.7566000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9626</v>
+        <v>-0.6254</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2781</v>
+        <v>-0.1313</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0939</v>
+        <v>-0.5597</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0939</v>
+        <v>-0.5597</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1468</v>
+        <v>-0.1969</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1312</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2781</v>
+        <v>-0.1313</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.5668</v>
+        <v>0.1958</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3917</v>
+        <v>0.1958</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2076</v>
+        <v>0.456</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.517</v>
+        <v>-0.2541</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3094</v>
+        <v>0.71</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>H. PALOMARES BARRADO</t>
+          <t>I. SAMA PEREZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5548</v>
+        <v>-0.2752</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7008</v>
+        <v>-0.8861</v>
       </c>
       <c r="F21" t="n">
-        <v>0.146</v>
+        <v>0.6108</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4362</v>
+        <v>-1.716</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1096</v>
+        <v>2.7452</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5458</v>
+        <v>-4.4612</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6414</v>
+        <v>-0.3285</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0408</v>
+        <v>2.4004</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6822</v>
+        <v>-2.7289</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2052</v>
+        <v>-1.3875</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0687</v>
+        <v>0.3448</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1364</v>
+        <v>-1.7323</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1958</v>
+        <v>1.5668</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1958</v>
+        <v>1.5668</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3145</v>
+        <v>-0.126</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0594</v>
+        <v>-0.5576</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2551</v>
+        <v>0.4316</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. SAMA PEREZ</t>
+          <t>H. PALOMARES BARRADO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9206</v>
+        <v>-0.3234</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3977</v>
+        <v>-0.4961</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4772</v>
+        <v>0.1727</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.716</v>
+        <v>-0.4362</v>
       </c>
       <c r="H22" t="n">
-        <v>2.7452</v>
+        <v>0.1096</v>
       </c>
       <c r="I22" t="n">
-        <v>-4.4612</v>
+        <v>-0.5458</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3285</v>
+        <v>-0.6414</v>
       </c>
       <c r="K22" t="n">
-        <v>2.4004</v>
+        <v>0.0408</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.7289</v>
+        <v>-0.6822</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3875</v>
+        <v>0.2052</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3448</v>
+        <v>0.0687</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.7323</v>
+        <v>0.1364</v>
       </c>
       <c r="P22" t="n">
-        <v>1.5668</v>
+        <v>0.1958</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5668</v>
+        <v>0.1958</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7713</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0692</v>
+        <v>0.1453</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2979</v>
+        <v>-0.2283</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.1614</v>
+        <v>-3.6866</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.8326</v>
+        <v>-3.6279</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3288</v>
+        <v>-0.0587</v>
       </c>
       <c r="G23" t="n">
         <v>-4.0321</v>
@@ -2248,13 +2248,13 @@
         <v>1.9585</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5578</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4817</v>
+        <v>-0.277</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0762</v>
+        <v>0.1939</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5507</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>3.883399999999998</v>
+        <v>4.565700000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.6886999999999999</v>
+        <v>-0.6885999999999997</v>
       </c>
       <c r="F24" t="n">
-        <v>4.571999999999999</v>
+        <v>5.2542</v>
       </c>
       <c r="G24" t="n">
         <v>-3.2295</v>
@@ -2299,7 +2299,7 @@
         <v>-14.1194</v>
       </c>
       <c r="J24" t="n">
-        <v>9.713299999999998</v>
+        <v>9.7133</v>
       </c>
       <c r="K24" t="n">
         <v>12.546</v>
@@ -2326,16 +2326,16 @@
         <v>14.6886</v>
       </c>
       <c r="S24" t="n">
-        <v>1.4851</v>
+        <v>2.1672</v>
       </c>
       <c r="T24" t="n">
         <v>-2.3849</v>
       </c>
       <c r="U24" t="n">
-        <v>3.869899999999999</v>
+        <v>4.552199999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>4.648699999999999</v>
+        <v>4.6487</v>
       </c>
       <c r="W24" t="n">
         <v>5.6925</v>
